--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11658,6 +11658,66 @@
         <v>355.14</v>
       </c>
       <c r="H374" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="n">
+        <v>331.7</v>
+      </c>
+      <c r="C375" t="n">
+        <v>338.41</v>
+      </c>
+      <c r="D375" t="n">
+        <v>347.77</v>
+      </c>
+      <c r="E375" t="n">
+        <v>352.91</v>
+      </c>
+      <c r="F375" t="n">
+        <v>352.6</v>
+      </c>
+      <c r="G375" t="n">
+        <v>354.96</v>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="n">
+        <v>332.23</v>
+      </c>
+      <c r="C376" t="n">
+        <v>339.61</v>
+      </c>
+      <c r="D376" t="n">
+        <v>347.43</v>
+      </c>
+      <c r="E376" t="n">
+        <v>353.11</v>
+      </c>
+      <c r="F376" t="n">
+        <v>353.85</v>
+      </c>
+      <c r="G376" t="n">
+        <v>356.65</v>
+      </c>
+      <c r="H376" t="inlineStr">
         <is>
           <t>L8</t>
         </is>
@@ -11674,7 +11734,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B389"/>
+  <dimension ref="A1:B391"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15567,6 +15627,26 @@
       </c>
       <c r="B389" t="n">
         <v>-0.4</v>
+      </c>
+    </row>
+    <row r="390">
+      <c r="A390" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B390" t="n">
+        <v>-0.6</v>
+      </c>
+    </row>
+    <row r="391">
+      <c r="A391" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B391" t="n">
+        <v>0.52</v>
       </c>
     </row>
   </sheetData>
@@ -15735,28 +15815,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.274585000041694</v>
+        <v>0.2761488328743029</v>
       </c>
       <c r="J2" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K2" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1196995760475972</v>
+        <v>0.1220990779798634</v>
       </c>
       <c r="M2" t="n">
-        <v>4.330946156490297</v>
+        <v>4.314091826669293</v>
       </c>
       <c r="N2" t="n">
-        <v>30.32558042949115</v>
+        <v>30.17571973619946</v>
       </c>
       <c r="O2" t="n">
-        <v>5.506866661677142</v>
+        <v>5.49324309822526</v>
       </c>
       <c r="P2" t="n">
-        <v>323.2142768497312</v>
+        <v>323.1978113955176</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15813,28 +15893,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3313124162211776</v>
+        <v>0.3372742603793631</v>
       </c>
       <c r="J3" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K3" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09393863616286935</v>
+        <v>0.09778173226669762</v>
       </c>
       <c r="M3" t="n">
-        <v>6.190378217515719</v>
+        <v>6.182691141216289</v>
       </c>
       <c r="N3" t="n">
-        <v>57.90365653431681</v>
+        <v>57.76414896192922</v>
       </c>
       <c r="O3" t="n">
-        <v>7.609445218563362</v>
+        <v>7.600272953120119</v>
       </c>
       <c r="P3" t="n">
-        <v>324.590414076787</v>
+        <v>324.5276444696225</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15891,28 +15971,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1810222697401825</v>
+        <v>0.1863552706238483</v>
       </c>
       <c r="J4" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K4" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L4" t="n">
-        <v>0.04862149680220984</v>
+        <v>0.05175935691690692</v>
       </c>
       <c r="M4" t="n">
-        <v>4.647998681823973</v>
+        <v>4.65282052680976</v>
       </c>
       <c r="N4" t="n">
-        <v>35.06761475568132</v>
+        <v>35.01475946599376</v>
       </c>
       <c r="O4" t="n">
-        <v>5.92179151572236</v>
+        <v>5.917327054168442</v>
       </c>
       <c r="P4" t="n">
-        <v>337.7522462897752</v>
+        <v>337.6961012588521</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -15969,28 +16049,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2169928014407722</v>
+        <v>0.2197170725451406</v>
       </c>
       <c r="J5" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K5" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L5" t="n">
-        <v>0.08699273972496324</v>
+        <v>0.0898346773375488</v>
       </c>
       <c r="M5" t="n">
-        <v>3.834553314358139</v>
+        <v>3.826442035473667</v>
       </c>
       <c r="N5" t="n">
-        <v>27.02707713207293</v>
+        <v>26.91794944558176</v>
       </c>
       <c r="O5" t="n">
-        <v>5.198757268047137</v>
+        <v>5.188251097005788</v>
       </c>
       <c r="P5" t="n">
-        <v>344.6886331167824</v>
+        <v>344.6599514091851</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16047,28 +16127,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2931640315949952</v>
+        <v>0.2986511678343504</v>
       </c>
       <c r="J6" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K6" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1211046799252141</v>
+        <v>0.1259181839609969</v>
       </c>
       <c r="M6" t="n">
-        <v>4.693148745379129</v>
+        <v>4.694608853012436</v>
       </c>
       <c r="N6" t="n">
-        <v>34.1125984361033</v>
+        <v>34.07455252648173</v>
       </c>
       <c r="O6" t="n">
-        <v>5.840599150438532</v>
+        <v>5.837341220665598</v>
       </c>
       <c r="P6" t="n">
-        <v>340.262045966696</v>
+        <v>340.2042739434875</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16125,28 +16205,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2006071142953516</v>
+        <v>0.2071854936215615</v>
       </c>
       <c r="J7" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="K7" t="n">
-        <v>373</v>
+        <v>375</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07107419018571026</v>
+        <v>0.07576081436000826</v>
       </c>
       <c r="M7" t="n">
-        <v>4.359553828565894</v>
+        <v>4.367909729819036</v>
       </c>
       <c r="N7" t="n">
-        <v>28.76596688864295</v>
+        <v>28.82016911196342</v>
       </c>
       <c r="O7" t="n">
-        <v>5.363391360757012</v>
+        <v>5.368441963173619</v>
       </c>
       <c r="P7" t="n">
-        <v>344.2586221706009</v>
+        <v>344.189360334967</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16184,7 +16264,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H374"/>
+  <dimension ref="A1:H376"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -31895,6 +31975,90 @@
         </is>
       </c>
     </row>
+    <row r="375">
+      <c r="A375" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-01 22:06:25+00:00</t>
+        </is>
+      </c>
+      <c r="B375" t="inlineStr">
+        <is>
+          <t>-36.772419415594335,175.7487424095277</t>
+        </is>
+      </c>
+      <c r="C375" t="inlineStr">
+        <is>
+          <t>-36.77313331720782,175.74861652624043</t>
+        </is>
+      </c>
+      <c r="D375" t="inlineStr">
+        <is>
+          <t>-36.773852543205024,175.7485195131438</t>
+        </is>
+      </c>
+      <c r="E375" t="inlineStr">
+        <is>
+          <t>-36.77456780267168,175.74838281289618</t>
+        </is>
+      </c>
+      <c r="F375" t="inlineStr">
+        <is>
+          <t>-36.775285773597574,175.7482731455993</t>
+        </is>
+      </c>
+      <c r="G375" t="inlineStr">
+        <is>
+          <t>-36.77600337597026,175.74820713412072</t>
+        </is>
+      </c>
+      <c r="H375" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="376">
+      <c r="A376" s="1" t="inlineStr">
+        <is>
+          <t>2026-01-09 22:05:44+00:00</t>
+        </is>
+      </c>
+      <c r="B376" t="inlineStr">
+        <is>
+          <t>-36.7724203868196,175.74874822003676</t>
+        </is>
+      </c>
+      <c r="C376" t="inlineStr">
+        <is>
+          <t>-36.77313551621028,175.74862968223266</t>
+        </is>
+      </c>
+      <c r="D376" t="inlineStr">
+        <is>
+          <t>-36.773851933364135,175.7485157822036</t>
+        </is>
+      </c>
+      <c r="E376" t="inlineStr">
+        <is>
+          <t>-36.774568066772105,175.74838502823863</t>
+        </is>
+      </c>
+      <c r="F376" t="inlineStr">
+        <is>
+          <t>-36.77528679821426,175.74828708475866</t>
+        </is>
+      </c>
+      <c r="G376" t="inlineStr">
+        <is>
+          <t>-36.77600465361488,175.74822599178825</t>
+        </is>
+      </c>
+      <c r="H376" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11720,6 +11720,66 @@
       <c r="H376" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="n">
+        <v>332.53</v>
+      </c>
+      <c r="C377" t="n">
+        <v>341.08</v>
+      </c>
+      <c r="D377" t="n">
+        <v>347.57</v>
+      </c>
+      <c r="E377" t="n">
+        <v>353.98</v>
+      </c>
+      <c r="F377" t="n">
+        <v>356.84</v>
+      </c>
+      <c r="G377" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="n">
+        <v>333.99</v>
+      </c>
+      <c r="C378" t="n">
+        <v>342.46</v>
+      </c>
+      <c r="D378" t="n">
+        <v>347.36</v>
+      </c>
+      <c r="E378" t="n">
+        <v>354.57</v>
+      </c>
+      <c r="F378" t="n">
+        <v>358.36</v>
+      </c>
+      <c r="G378" t="n">
+        <v>357.58</v>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11734,7 +11794,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B391"/>
+  <dimension ref="A1:B393"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15647,6 +15707,26 @@
       </c>
       <c r="B391" t="n">
         <v>0.52</v>
+      </c>
+    </row>
+    <row r="392">
+      <c r="A392" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B392" t="n">
+        <v>-0.42</v>
+      </c>
+    </row>
+    <row r="393">
+      <c r="A393" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B393" t="n">
+        <v>0.78</v>
       </c>
     </row>
   </sheetData>
@@ -15815,28 +15895,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2761488328743029</v>
+        <v>0.278997700551752</v>
       </c>
       <c r="J2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K2" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1220990779798634</v>
+        <v>0.1254434292743828</v>
       </c>
       <c r="M2" t="n">
-        <v>4.314091826669293</v>
+        <v>4.302407665608805</v>
       </c>
       <c r="N2" t="n">
-        <v>30.17571973619946</v>
+        <v>30.05669289312131</v>
       </c>
       <c r="O2" t="n">
-        <v>5.49324309822526</v>
+        <v>5.482398461724696</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1978113955176</v>
+        <v>323.1676145688685</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15893,28 +15973,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3372742603793631</v>
+        <v>0.3459632213412467</v>
       </c>
       <c r="J3" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K3" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L3" t="n">
-        <v>0.09778173226669762</v>
+        <v>0.1028652068511218</v>
       </c>
       <c r="M3" t="n">
-        <v>6.182691141216289</v>
+        <v>6.18678092261456</v>
       </c>
       <c r="N3" t="n">
-        <v>57.76414896192922</v>
+        <v>57.81612993505362</v>
       </c>
       <c r="O3" t="n">
-        <v>7.600272953120119</v>
+        <v>7.603691862184687</v>
       </c>
       <c r="P3" t="n">
-        <v>324.5276444696225</v>
+        <v>324.4355531563581</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -15971,28 +16051,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1863552706238483</v>
+        <v>0.1914124731206944</v>
       </c>
       <c r="J4" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K4" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05175935691690692</v>
+        <v>0.05487646051652872</v>
       </c>
       <c r="M4" t="n">
-        <v>4.65282052680976</v>
+        <v>4.655774897804493</v>
       </c>
       <c r="N4" t="n">
-        <v>35.01475946599376</v>
+        <v>34.94965668348342</v>
       </c>
       <c r="O4" t="n">
-        <v>5.917327054168442</v>
+        <v>5.911823465182584</v>
       </c>
       <c r="P4" t="n">
-        <v>337.6961012588521</v>
+        <v>337.642504398228</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16049,28 +16129,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2197170725451406</v>
+        <v>0.2236794251718694</v>
       </c>
       <c r="J5" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K5" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L5" t="n">
-        <v>0.0898346773375488</v>
+        <v>0.09355270217493161</v>
       </c>
       <c r="M5" t="n">
-        <v>3.826442035473667</v>
+        <v>3.824064159885777</v>
       </c>
       <c r="N5" t="n">
-        <v>26.91794944558176</v>
+        <v>26.84962691186475</v>
       </c>
       <c r="O5" t="n">
-        <v>5.188251097005788</v>
+        <v>5.181662562524189</v>
       </c>
       <c r="P5" t="n">
-        <v>344.6599514091851</v>
+        <v>344.6179558897736</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16127,28 +16207,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.2986511678343504</v>
+        <v>0.3085826419808634</v>
       </c>
       <c r="J6" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K6" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1259181839609969</v>
+        <v>0.1330622503567404</v>
       </c>
       <c r="M6" t="n">
-        <v>4.694608853012436</v>
+        <v>4.71673528735161</v>
       </c>
       <c r="N6" t="n">
-        <v>34.07455252648173</v>
+        <v>34.36180691007626</v>
       </c>
       <c r="O6" t="n">
-        <v>5.837341220665598</v>
+        <v>5.861894481315427</v>
       </c>
       <c r="P6" t="n">
-        <v>340.2042739434875</v>
+        <v>340.0990138152844</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16205,28 +16285,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2071854936215615</v>
+        <v>0.2158785304426833</v>
       </c>
       <c r="J7" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="K7" t="n">
-        <v>375</v>
+        <v>377</v>
       </c>
       <c r="L7" t="n">
-        <v>0.07576081436000826</v>
+        <v>0.08166852976608174</v>
       </c>
       <c r="M7" t="n">
-        <v>4.367909729819036</v>
+        <v>4.385727216010236</v>
       </c>
       <c r="N7" t="n">
-        <v>28.82016911196342</v>
+        <v>29.02442288103722</v>
       </c>
       <c r="O7" t="n">
-        <v>5.368441963173619</v>
+        <v>5.387431937485356</v>
       </c>
       <c r="P7" t="n">
-        <v>344.189360334967</v>
+        <v>344.0972315402327</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16264,7 +16344,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H376"/>
+  <dimension ref="A1:H378"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32059,6 +32139,90 @@
         </is>
       </c>
     </row>
+    <row r="377">
+      <c r="A377" s="1" t="inlineStr">
+        <is>
+          <t>2026-02-26 22:05:37+00:00</t>
+        </is>
+      </c>
+      <c r="B377" t="inlineStr">
+        <is>
+          <t>-36.77242093656962,175.74875150900422</t>
+        </is>
+      </c>
+      <c r="C377" t="inlineStr">
+        <is>
+          <t>-36.77313820998624,175.74864579832402</t>
+        </is>
+      </c>
+      <c r="D377" t="inlineStr">
+        <is>
+          <t>-36.77385218447511,175.7485173184731</t>
+        </is>
+      </c>
+      <c r="E377" t="inlineStr">
+        <is>
+          <t>-36.774569215608516,175.7483946649785</t>
+        </is>
+      </c>
+      <c r="F377" t="inlineStr">
+        <is>
+          <t>-36.77528924909072,175.7483204272289</t>
+        </is>
+      </c>
+      <c r="G377" t="inlineStr">
+        <is>
+          <t>-36.77600594637649,175.7482450726239</t>
+        </is>
+      </c>
+      <c r="H377" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="378">
+      <c r="A378" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-06 22:06:08+00:00</t>
+        </is>
+      </c>
+      <c r="B378" t="inlineStr">
+        <is>
+          <t>-36.77242361201839,175.74876751531312</t>
+        </is>
+      </c>
+      <c r="C378" t="inlineStr">
+        <is>
+          <t>-36.77314073883513,175.74866092771686</t>
+        </is>
+      </c>
+      <c r="D378" t="inlineStr">
+        <is>
+          <t>-36.773851807808654,175.74851501406886</t>
+        </is>
+      </c>
+      <c r="E378" t="inlineStr">
+        <is>
+          <t>-36.77456999470401,175.748401200239</t>
+        </is>
+      </c>
+      <c r="F378" t="inlineStr">
+        <is>
+          <t>-36.77529049501761,175.7483373772478</t>
+        </is>
+      </c>
+      <c r="G378" t="inlineStr">
+        <is>
+          <t>-36.77600535669614,175.74823636908476</t>
+        </is>
+      </c>
+      <c r="H378" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H378"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11780,6 +11780,36 @@
       <c r="H378" t="inlineStr">
         <is>
           <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="n">
+        <v>333.34</v>
+      </c>
+      <c r="C379" t="n">
+        <v>341.05</v>
+      </c>
+      <c r="D379" t="n">
+        <v>346.11</v>
+      </c>
+      <c r="E379" t="n">
+        <v>353.5</v>
+      </c>
+      <c r="F379" t="n">
+        <v>356.96</v>
+      </c>
+      <c r="G379" t="n">
+        <v>356.16</v>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>L8</t>
         </is>
       </c>
     </row>
@@ -11794,7 +11824,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B393"/>
+  <dimension ref="A1:B394"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15727,6 +15757,16 @@
       </c>
       <c r="B393" t="n">
         <v>0.78</v>
+      </c>
+    </row>
+    <row r="394">
+      <c r="A394" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B394" t="n">
+        <v>-0.42</v>
       </c>
     </row>
   </sheetData>
@@ -15895,28 +15935,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.278997700551752</v>
+        <v>0.2804271394112258</v>
       </c>
       <c r="J2" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K2" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1254434292743828</v>
+        <v>0.1271365225817622</v>
       </c>
       <c r="M2" t="n">
-        <v>4.302407665608805</v>
+        <v>4.296618283543483</v>
       </c>
       <c r="N2" t="n">
-        <v>30.05669289312131</v>
+        <v>29.9967720879062</v>
       </c>
       <c r="O2" t="n">
-        <v>5.482398461724696</v>
+        <v>5.47693090041368</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1676145688685</v>
+        <v>323.1524435287756</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -15973,28 +16013,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3459632213412467</v>
+        <v>0.3498271226519936</v>
       </c>
       <c r="J3" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K3" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1028652068511218</v>
+        <v>0.1052433829842732</v>
       </c>
       <c r="M3" t="n">
-        <v>6.18678092261456</v>
+        <v>6.18693703774921</v>
       </c>
       <c r="N3" t="n">
-        <v>57.81612993505362</v>
+        <v>57.80634642600426</v>
       </c>
       <c r="O3" t="n">
-        <v>7.603691862184687</v>
+        <v>7.603048495570988</v>
       </c>
       <c r="P3" t="n">
-        <v>324.4355531563581</v>
+        <v>324.3945444757056</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16051,28 +16091,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1914124731206944</v>
+        <v>0.1931739082043427</v>
       </c>
       <c r="J4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K4" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05487646051652872</v>
+        <v>0.05609457412028307</v>
       </c>
       <c r="M4" t="n">
-        <v>4.655774897804493</v>
+        <v>4.653079502299018</v>
       </c>
       <c r="N4" t="n">
-        <v>34.94965668348342</v>
+        <v>34.88695028228507</v>
       </c>
       <c r="O4" t="n">
-        <v>5.911823465182584</v>
+        <v>5.906517610427067</v>
       </c>
       <c r="P4" t="n">
-        <v>337.642504398228</v>
+        <v>337.6238097880333</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16129,28 +16169,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2236794251718694</v>
+        <v>0.2252072642900183</v>
       </c>
       <c r="J5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K5" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09355270217493161</v>
+        <v>0.09513817429587745</v>
       </c>
       <c r="M5" t="n">
-        <v>3.824064159885777</v>
+        <v>3.820880780260332</v>
       </c>
       <c r="N5" t="n">
-        <v>26.84962691186475</v>
+        <v>26.8009809336144</v>
       </c>
       <c r="O5" t="n">
-        <v>5.181662562524189</v>
+        <v>5.176966383280308</v>
       </c>
       <c r="P5" t="n">
-        <v>344.6179558897736</v>
+        <v>344.6017404998229</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16207,28 +16247,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3085826419808634</v>
+        <v>0.3130992546949463</v>
       </c>
       <c r="J6" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K6" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1330622503567404</v>
+        <v>0.1364605642951374</v>
       </c>
       <c r="M6" t="n">
-        <v>4.71673528735161</v>
+        <v>4.725610714374193</v>
       </c>
       <c r="N6" t="n">
-        <v>34.36180691007626</v>
+        <v>34.46652718394834</v>
       </c>
       <c r="O6" t="n">
-        <v>5.861894481315427</v>
+        <v>5.870819975433444</v>
       </c>
       <c r="P6" t="n">
-        <v>340.0990138152844</v>
+        <v>340.0510777233591</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16285,28 +16325,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2158785304426833</v>
+        <v>0.2191779906233801</v>
       </c>
       <c r="J7" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="K7" t="n">
-        <v>377</v>
+        <v>378</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08166852976608174</v>
+        <v>0.08414041876066325</v>
       </c>
       <c r="M7" t="n">
-        <v>4.385727216010236</v>
+        <v>4.389655554828315</v>
       </c>
       <c r="N7" t="n">
-        <v>29.02442288103722</v>
+        <v>29.05203457791918</v>
       </c>
       <c r="O7" t="n">
-        <v>5.387431937485356</v>
+        <v>5.389993931157917</v>
       </c>
       <c r="P7" t="n">
-        <v>344.0972315402327</v>
+        <v>344.0622134334039</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16344,7 +16384,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H378"/>
+  <dimension ref="A1:H379"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32223,6 +32263,48 @@
         </is>
       </c>
     </row>
+    <row r="379">
+      <c r="A379" s="1" t="inlineStr">
+        <is>
+          <t>2026-03-14 22:05:50+00:00</t>
+        </is>
+      </c>
+      <c r="B379" t="inlineStr">
+        <is>
+          <t>-36.77242242089421,175.74876038921656</t>
+        </is>
+      </c>
+      <c r="C379" t="inlineStr">
+        <is>
+          <t>-36.77313815501125,175.7486454694242</t>
+        </is>
+      </c>
+      <c r="D379" t="inlineStr">
+        <is>
+          <t>-36.77384956574543,175.74850129737746</t>
+        </is>
+      </c>
+      <c r="E379" t="inlineStr">
+        <is>
+          <t>-36.774568581767845,175.74838934815648</t>
+        </is>
+      </c>
+      <c r="F379" t="inlineStr">
+        <is>
+          <t>-36.775289347453466,175.74832176538825</t>
+        </is>
+      </c>
+      <c r="G379" t="inlineStr">
+        <is>
+          <t>-36.77600428317385,175.74822052418045</t>
+        </is>
+      </c>
+      <c r="H379" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H379"/>
+  <dimension ref="A1:H381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11810,6 +11810,66 @@
       <c r="H379" t="inlineStr">
         <is>
           <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="n">
+        <v>331.05</v>
+      </c>
+      <c r="C380" t="n">
+        <v>339.23</v>
+      </c>
+      <c r="D380" t="n">
+        <v>340.69</v>
+      </c>
+      <c r="E380" t="n">
+        <v>351.17</v>
+      </c>
+      <c r="F380" t="n">
+        <v>351.9</v>
+      </c>
+      <c r="G380" t="n">
+        <v>352.24</v>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="n">
+        <v>330.34</v>
+      </c>
+      <c r="C381" t="n">
+        <v>338.46</v>
+      </c>
+      <c r="D381" t="n">
+        <v>342.13</v>
+      </c>
+      <c r="E381" t="n">
+        <v>350.62</v>
+      </c>
+      <c r="F381" t="n">
+        <v>351.55</v>
+      </c>
+      <c r="G381" t="n">
+        <v>352.2</v>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>L9</t>
         </is>
       </c>
     </row>
@@ -11824,7 +11884,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B394"/>
+  <dimension ref="A1:B396"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15767,6 +15827,26 @@
       </c>
       <c r="B394" t="n">
         <v>-0.42</v>
+      </c>
+    </row>
+    <row r="395">
+      <c r="A395" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B395" t="n">
+        <v>0.08</v>
+      </c>
+    </row>
+    <row r="396">
+      <c r="A396" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B396" t="n">
+        <v>-0.54</v>
       </c>
     </row>
   </sheetData>
@@ -15935,28 +16015,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2804271394112258</v>
+        <v>0.2804379813656933</v>
       </c>
       <c r="J2" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K2" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L2" t="n">
-        <v>0.1271365225817622</v>
+        <v>0.128452443553329</v>
       </c>
       <c r="M2" t="n">
-        <v>4.296618283543483</v>
+        <v>4.27587473487961</v>
       </c>
       <c r="N2" t="n">
-        <v>29.9967720879062</v>
+        <v>29.8395684048471</v>
       </c>
       <c r="O2" t="n">
-        <v>5.47693090041368</v>
+        <v>5.462560608803082</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1524435287756</v>
+        <v>323.1523294015975</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16013,28 +16093,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.3498271226519936</v>
+        <v>0.35511768370209</v>
       </c>
       <c r="J3" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K3" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L3" t="n">
-        <v>0.1052433829842732</v>
+        <v>0.10901723314421</v>
       </c>
       <c r="M3" t="n">
-        <v>6.18693703774921</v>
+        <v>6.17665883307069</v>
       </c>
       <c r="N3" t="n">
-        <v>57.80634642600426</v>
+        <v>57.63534544795056</v>
       </c>
       <c r="O3" t="n">
-        <v>7.603048495570988</v>
+        <v>7.591794613130057</v>
       </c>
       <c r="P3" t="n">
-        <v>324.3945444757056</v>
+        <v>324.3379502902741</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16091,28 +16171,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.1931739082043427</v>
+        <v>0.191706721561359</v>
       </c>
       <c r="J4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K4" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05609457412028307</v>
+        <v>0.05589007179996119</v>
       </c>
       <c r="M4" t="n">
-        <v>4.653079502299018</v>
+        <v>4.635254760587704</v>
       </c>
       <c r="N4" t="n">
-        <v>34.88695028228507</v>
+        <v>34.71624390340047</v>
       </c>
       <c r="O4" t="n">
-        <v>5.906517610427067</v>
+        <v>5.892049210877356</v>
       </c>
       <c r="P4" t="n">
-        <v>337.6238097880333</v>
+        <v>337.6395014137775</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16169,28 +16249,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2252072642900183</v>
+        <v>0.2254665037559283</v>
       </c>
       <c r="J5" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K5" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09513817429587745</v>
+        <v>0.09635243327551135</v>
       </c>
       <c r="M5" t="n">
-        <v>3.820880780260332</v>
+        <v>3.802100858244207</v>
       </c>
       <c r="N5" t="n">
-        <v>26.8009809336144</v>
+        <v>26.66064246777011</v>
       </c>
       <c r="O5" t="n">
-        <v>5.176966383280308</v>
+        <v>5.163394471447065</v>
       </c>
       <c r="P5" t="n">
-        <v>344.6017404998229</v>
+        <v>344.5989686952737</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16247,28 +16327,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3130992546949463</v>
+        <v>0.3165201526796095</v>
       </c>
       <c r="J6" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K6" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1364605642951374</v>
+        <v>0.1402593282169466</v>
       </c>
       <c r="M6" t="n">
-        <v>4.725610714374193</v>
+        <v>4.716558099424213</v>
       </c>
       <c r="N6" t="n">
-        <v>34.46652718394834</v>
+        <v>34.34065735926479</v>
       </c>
       <c r="O6" t="n">
-        <v>5.870819975433444</v>
+        <v>5.86009021767283</v>
       </c>
       <c r="P6" t="n">
-        <v>340.0510777233591</v>
+        <v>340.0144833001641</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16325,28 +16405,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2191779906233801</v>
+        <v>0.2215570127484936</v>
       </c>
       <c r="J7" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="K7" t="n">
-        <v>378</v>
+        <v>380</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08414041876066325</v>
+        <v>0.08667238492273011</v>
       </c>
       <c r="M7" t="n">
-        <v>4.389655554828315</v>
+        <v>4.377511635043614</v>
       </c>
       <c r="N7" t="n">
-        <v>29.05203457791918</v>
+        <v>28.92590777242494</v>
       </c>
       <c r="O7" t="n">
-        <v>5.389993931157917</v>
+        <v>5.378281116902029</v>
       </c>
       <c r="P7" t="n">
-        <v>344.0622134334039</v>
+        <v>344.0367637716282</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16384,7 +16464,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H379"/>
+  <dimension ref="A1:H381"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32305,6 +32385,90 @@
         </is>
       </c>
     </row>
+    <row r="380">
+      <c r="A380" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-17 22:05:08+00:00</t>
+        </is>
+      </c>
+      <c r="B380" t="inlineStr">
+        <is>
+          <t>-36.77241822446861,175.7487352834318</t>
+        </is>
+      </c>
+      <c r="C380" t="inlineStr">
+        <is>
+          <t>-36.77313481985966,175.74862551616837</t>
+        </is>
+      </c>
+      <c r="D380" t="inlineStr">
+        <is>
+          <t>-36.77383984414063,175.7484418218117</t>
+        </is>
+      </c>
+      <c r="E380" t="inlineStr">
+        <is>
+          <t>-36.774565504996126,175.74836353941728</t>
+        </is>
+      </c>
+      <c r="F380" t="inlineStr">
+        <is>
+          <t>-36.775285199811485,175.74826533967018</t>
+        </is>
+      </c>
+      <c r="G380" t="inlineStr">
+        <is>
+          <t>-36.77600131963649,175.74817678331948</t>
+        </is>
+      </c>
+      <c r="H380" t="inlineStr">
+        <is>
+          <t>L8</t>
+        </is>
+      </c>
+    </row>
+    <row r="381">
+      <c r="A381" s="1" t="inlineStr">
+        <is>
+          <t>2026-05-25 22:05:20+00:00</t>
+        </is>
+      </c>
+      <c r="B381" t="inlineStr">
+        <is>
+          <t>-36.772416923392335,175.74872749954272</t>
+        </is>
+      </c>
+      <c r="C381" t="inlineStr">
+        <is>
+          <t>-36.77313340883295,175.74861707440672</t>
+        </is>
+      </c>
+      <c r="D381" t="inlineStr">
+        <is>
+          <t>-36.77384242700539,175.74845762343674</t>
+        </is>
+      </c>
+      <c r="E381" t="inlineStr">
+        <is>
+          <t>-36.77456477871871,175.7483574472259</t>
+        </is>
+      </c>
+      <c r="F381" t="inlineStr">
+        <is>
+          <t>-36.775284912918245,175.74826143670566</t>
+        </is>
+      </c>
+      <c r="G381" t="inlineStr">
+        <is>
+          <t>-36.77600128939623,175.74817633698416</t>
+        </is>
+      </c>
+      <c r="H381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/data/nzd0170/nzd0170.xlsx
+++ b/data/nzd0170/nzd0170.xlsx
@@ -428,7 +428,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H381"/>
+  <dimension ref="A1:H382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -11868,6 +11868,36 @@
         <v>352.2</v>
       </c>
       <c r="H381" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="n">
+        <v>330.03</v>
+      </c>
+      <c r="C382" t="n">
+        <v>338.57</v>
+      </c>
+      <c r="D382" t="n">
+        <v>343.53</v>
+      </c>
+      <c r="E382" t="n">
+        <v>350.38</v>
+      </c>
+      <c r="F382" t="n">
+        <v>351.56</v>
+      </c>
+      <c r="G382" t="n">
+        <v>353.02</v>
+      </c>
+      <c r="H382" t="inlineStr">
         <is>
           <t>L9</t>
         </is>
@@ -11884,7 +11914,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:B396"/>
+  <dimension ref="A1:B397"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -15847,6 +15877,16 @@
       </c>
       <c r="B396" t="n">
         <v>-0.54</v>
+      </c>
+    </row>
+    <row r="397">
+      <c r="A397" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:10:00+00:00</t>
+        </is>
+      </c>
+      <c r="B397" t="n">
+        <v>-0.55</v>
       </c>
     </row>
   </sheetData>
@@ -16015,28 +16055,28 @@
         <v>0.1132</v>
       </c>
       <c r="I2" t="n">
-        <v>0.2804379813656933</v>
+        <v>0.2800894328810278</v>
       </c>
       <c r="J2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K2" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L2" t="n">
-        <v>0.128452443553329</v>
+        <v>0.1288233517509536</v>
       </c>
       <c r="M2" t="n">
-        <v>4.27587473487961</v>
+        <v>4.266784202464102</v>
       </c>
       <c r="N2" t="n">
-        <v>29.8395684048471</v>
+        <v>29.76241385161225</v>
       </c>
       <c r="O2" t="n">
-        <v>5.462560608803082</v>
+        <v>5.455493914542684</v>
       </c>
       <c r="P2" t="n">
-        <v>323.1523294015975</v>
+        <v>323.1560666295177</v>
       </c>
       <c r="Q2" t="inlineStr"/>
       <c r="R2" t="inlineStr">
@@ -16093,28 +16133,28 @@
         <v>0.1448</v>
       </c>
       <c r="I3" t="n">
-        <v>0.35511768370209</v>
+        <v>0.3575558980070694</v>
       </c>
       <c r="J3" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K3" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L3" t="n">
-        <v>0.10901723314421</v>
+        <v>0.1108301350421089</v>
       </c>
       <c r="M3" t="n">
-        <v>6.17665883307069</v>
+        <v>6.170781999699841</v>
       </c>
       <c r="N3" t="n">
-        <v>57.63534544795056</v>
+        <v>57.54105726053503</v>
       </c>
       <c r="O3" t="n">
-        <v>7.591794613130057</v>
+        <v>7.585582196544641</v>
       </c>
       <c r="P3" t="n">
-        <v>324.3379502902741</v>
+        <v>324.311807119448</v>
       </c>
       <c r="Q3" t="inlineStr"/>
       <c r="R3" t="inlineStr">
@@ -16171,28 +16211,28 @@
         <v>0.1411</v>
       </c>
       <c r="I4" t="n">
-        <v>0.191706721561359</v>
+        <v>0.1920886493180304</v>
       </c>
       <c r="J4" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K4" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L4" t="n">
-        <v>0.05589007179996119</v>
+        <v>0.05640813927717059</v>
       </c>
       <c r="M4" t="n">
-        <v>4.635254760587704</v>
+        <v>4.625184474504879</v>
       </c>
       <c r="N4" t="n">
-        <v>34.71624390340047</v>
+        <v>34.62652340183968</v>
       </c>
       <c r="O4" t="n">
-        <v>5.892049210877356</v>
+        <v>5.884430592830515</v>
       </c>
       <c r="P4" t="n">
-        <v>337.6395014137775</v>
+        <v>337.6354062845817</v>
       </c>
       <c r="Q4" t="inlineStr"/>
       <c r="R4" t="inlineStr">
@@ -16249,28 +16289,28 @@
         <v>0.2</v>
       </c>
       <c r="I5" t="n">
-        <v>0.2254665037559283</v>
+        <v>0.2253169532446877</v>
       </c>
       <c r="J5" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K5" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L5" t="n">
-        <v>0.09635243327551135</v>
+        <v>0.09674498468541315</v>
       </c>
       <c r="M5" t="n">
-        <v>3.802100858244207</v>
+        <v>3.792938167238722</v>
       </c>
       <c r="N5" t="n">
-        <v>26.66064246777011</v>
+        <v>26.59088141491675</v>
       </c>
       <c r="O5" t="n">
-        <v>5.163394471447065</v>
+        <v>5.156634698610786</v>
       </c>
       <c r="P5" t="n">
-        <v>344.5989686952737</v>
+        <v>344.6005722149291</v>
       </c>
       <c r="Q5" t="inlineStr"/>
       <c r="R5" t="inlineStr">
@@ -16327,28 +16367,28 @@
         <v>0.1083</v>
       </c>
       <c r="I6" t="n">
-        <v>0.3165201526796095</v>
+        <v>0.3181014096233621</v>
       </c>
       <c r="J6" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K6" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L6" t="n">
-        <v>0.1402593282169466</v>
+        <v>0.142090406025013</v>
       </c>
       <c r="M6" t="n">
-        <v>4.716558099424213</v>
+        <v>4.71155915976405</v>
       </c>
       <c r="N6" t="n">
-        <v>34.34065735926479</v>
+        <v>34.27449213097842</v>
       </c>
       <c r="O6" t="n">
-        <v>5.86009021767283</v>
+        <v>5.854442085372304</v>
       </c>
       <c r="P6" t="n">
-        <v>340.0144833001641</v>
+        <v>339.9975286500679</v>
       </c>
       <c r="Q6" t="inlineStr"/>
       <c r="R6" t="inlineStr">
@@ -16405,28 +16445,28 @@
         <v>0.1275</v>
       </c>
       <c r="I7" t="n">
-        <v>0.2215570127484936</v>
+        <v>0.2231320070209644</v>
       </c>
       <c r="J7" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="K7" t="n">
-        <v>380</v>
+        <v>381</v>
       </c>
       <c r="L7" t="n">
-        <v>0.08667238492273011</v>
+        <v>0.08820266665504051</v>
       </c>
       <c r="M7" t="n">
-        <v>4.377511635043614</v>
+        <v>4.373286400106059</v>
       </c>
       <c r="N7" t="n">
-        <v>28.92590777242494</v>
+        <v>28.87376500974932</v>
       </c>
       <c r="O7" t="n">
-        <v>5.378281116902029</v>
+        <v>5.373431399929594</v>
       </c>
       <c r="P7" t="n">
-        <v>344.0367637716282</v>
+        <v>344.0198762715296</v>
       </c>
       <c r="Q7" t="inlineStr"/>
       <c r="R7" t="inlineStr">
@@ -16464,7 +16504,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:H381"/>
+  <dimension ref="A1:H382"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -32469,6 +32509,48 @@
         </is>
       </c>
     </row>
+    <row r="382">
+      <c r="A382" s="1" t="inlineStr">
+        <is>
+          <t>2026-06-10 22:05:18+00:00</t>
+        </is>
+      </c>
+      <c r="B382" t="inlineStr">
+        <is>
+          <t>-36.7724163553166,175.74872410094332</t>
+        </is>
+      </c>
+      <c r="C382" t="inlineStr">
+        <is>
+          <t>-36.77313361040823,175.74861828037265</t>
+        </is>
+      </c>
+      <c r="D382" t="inlineStr">
+        <is>
+          <t>-36.77384493812185,175.74847298612863</t>
+        </is>
+      </c>
+      <c r="E382" t="inlineStr">
+        <is>
+          <t>-36.77456446179756,175.74835478881513</t>
+        </is>
+      </c>
+      <c r="F382" t="inlineStr">
+        <is>
+          <t>-36.7752849211152,175.74826154821892</t>
+        </is>
+      </c>
+      <c r="G382" t="inlineStr">
+        <is>
+          <t>-36.77600190932124,175.74818548685795</t>
+        </is>
+      </c>
+      <c r="H382" t="inlineStr">
+        <is>
+          <t>L9</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
